--- a/artfynd/A 25374-2024 artfynd.xlsx
+++ b/artfynd/A 25374-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121633115</v>
+        <v>121633116</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581416</v>
+        <v>581153</v>
       </c>
       <c r="R2" t="n">
-        <v>7175240</v>
+        <v>7175589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121633116</v>
+        <v>121633115</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581153</v>
+        <v>581416</v>
       </c>
       <c r="R3" t="n">
-        <v>7175589</v>
+        <v>7175240</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 25374-2024 artfynd.xlsx
+++ b/artfynd/A 25374-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121633116</v>
+        <v>121633115</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581153</v>
+        <v>581416</v>
       </c>
       <c r="R2" t="n">
-        <v>7175589</v>
+        <v>7175240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121633115</v>
+        <v>121633116</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581416</v>
+        <v>581153</v>
       </c>
       <c r="R3" t="n">
-        <v>7175240</v>
+        <v>7175589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 25374-2024 artfynd.xlsx
+++ b/artfynd/A 25374-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121633116</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121633115</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 25374-2024 artfynd.xlsx
+++ b/artfynd/A 25374-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121633116</v>
+        <v>121633115</v>
       </c>
       <c r="B2" t="n">
         <v>57365</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581153</v>
+        <v>581416</v>
       </c>
       <c r="R2" t="n">
-        <v>7175589</v>
+        <v>7175240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121633115</v>
+        <v>121633116</v>
       </c>
       <c r="B3" t="n">
         <v>57365</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581416</v>
+        <v>581153</v>
       </c>
       <c r="R3" t="n">
-        <v>7175240</v>
+        <v>7175589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 25374-2024 artfynd.xlsx
+++ b/artfynd/A 25374-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121633115</v>
+        <v>121633116</v>
       </c>
       <c r="B2" t="n">
         <v>57365</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581416</v>
+        <v>581153</v>
       </c>
       <c r="R2" t="n">
-        <v>7175240</v>
+        <v>7175589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121633116</v>
+        <v>121633115</v>
       </c>
       <c r="B3" t="n">
         <v>57365</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581153</v>
+        <v>581416</v>
       </c>
       <c r="R3" t="n">
-        <v>7175589</v>
+        <v>7175240</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 25374-2024 artfynd.xlsx
+++ b/artfynd/A 25374-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121633116</v>
+        <v>121633115</v>
       </c>
       <c r="B2" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581153</v>
+        <v>581416</v>
       </c>
       <c r="R2" t="n">
-        <v>7175589</v>
+        <v>7175240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121633115</v>
+        <v>121633116</v>
       </c>
       <c r="B3" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581416</v>
+        <v>581153</v>
       </c>
       <c r="R3" t="n">
-        <v>7175240</v>
+        <v>7175589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
